--- a/Coding Track.xlsx
+++ b/Coding Track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E6B75D-F7C1-4EF4-9F8E-B6D19FA5CACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078CE86D-657B-4151-94C7-BFD21EDAD4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Category</t>
   </si>
@@ -55,6 +55,33 @@
   </si>
   <si>
     <t>https://github.com/meraviverma/coding_python/blob/main/NeetCode/Stack/MinStack.py</t>
+  </si>
+  <si>
+    <t>https://github.com/meraviverma/coding_python/blob/main/NeetCode/Stack/ReversePolishNotation.py</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iu0082c4HDE&amp;t=539s</t>
+  </si>
+  <si>
+    <t>https://neetcode.io/problems/evaluate-reverse-polish-notation/solution</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Day1</t>
+  </si>
+  <si>
+    <t>Day2</t>
   </si>
 </sst>
 </file>
@@ -122,10 +149,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -407,55 +435,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.06640625" customWidth="1"/>
-    <col min="3" max="3" width="56.53125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.19921875" customWidth="1"/>
+    <col min="4" max="4" width="30.06640625" customWidth="1"/>
+    <col min="5" max="5" width="59.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="85.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{F726BE23-D68C-4832-A901-61DD62B0C216}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{CC7039D2-2143-4B8A-945B-17D177548ED4}"/>
-    <hyperlink ref="D2" r:id="rId3" xr:uid="{35DAB5A4-2652-4258-A35B-590AC9072752}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{F726BE23-D68C-4832-A901-61DD62B0C216}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{CC7039D2-2143-4B8A-945B-17D177548ED4}"/>
+    <hyperlink ref="F2" r:id="rId3" xr:uid="{35DAB5A4-2652-4258-A35B-590AC9072752}"/>
+    <hyperlink ref="F3" r:id="rId4" xr:uid="{048A6874-B7EC-49FF-B01B-628FA5B6A05F}"/>
+    <hyperlink ref="G3" r:id="rId5" xr:uid="{147EEEAC-1B0D-43F7-9918-136F67341B59}"/>
+    <hyperlink ref="E3" r:id="rId6" xr:uid="{D8C3D6AB-9AA4-4232-8C4B-C79D63236DF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
